--- a/stories/arbres/ATOM-REL.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gisèle joue à la dinette. Les tasses sont lisses. Adèle veut la tasse bleue. Maman est près de la fenêtre. Gisèle prête la tasse. Elle attend son tour. Adèle verse de l'eau imaginaire. Puis c'est le tour de Gisèle. Elle pose une assiette. Maman dit : on peut prêter. On attend son tour. Ou on propose un autre jeu. Plus tard, au jardin, l'herbe est tiède. Adèle veut le cerceau. Gisèle dit : on peut prêter. Ou attendre son tour. Elle prête le cerceau. Elle propose les cubes. C'est un autre jeu. Adèle prend un cube. Gisèle attend. Puis elle joue. Même leçon dehors. Prêter. Tour. Autre jeu. Maman tape dans ses mains.</t>
+          <t>Gisèle joue à la dinette. Les tasses sont lisses. Adèle veut la tasse bleue. Maman est près de la fenêtre. Gisèle prête la tasse. Elle attend son tour. Adèle verse de l'eau imaginaire. Puis c'est le tour de Gisèle. Elle pose une assiette. On peut prêter. On attend son tour. Ou on propose un autre jeu. Plus tard, au jardin, l'herbe est tiède. Adèle veut le cerceau. On peut prêter. Ou attendre son tour. Elle prête le cerceau. Elle propose les cubes. C'est un autre jeu. Adèle prend un cube. Gisèle attend. Puis elle joue. Même leçon dehors. Prêter. Tour. Autre jeu. Maman tape dans ses mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gisèle joue à la dinette. Les tasses sont lisses. Adèle veut la tasse bleue. Maman est près de la fenêtre. Gisèle prête la tasse. Elle attend son tour. Adèle verse de l'eau imaginaire. Puis c'est le tour de Gisèle. Elle pose une assiette.
+maman|On peut prêter. On attend son tour. Ou on propose un autre jeu. Plus tard, au jardin, l'herbe est tiède.
+narrateur|Adèle veut le cerceau.
+enfant-f|On peut prêter. Ou attendre son tour. Elle prête le cerceau. Elle propose les cubes. C'est un autre jeu.
+narrateur|Adèle prend un cube. Gisèle attend. Puis elle joue. Même leçon dehors. Prêter. Tour. Autre jeu. Maman tape dans ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Adèle veut un jouet. Que peut faire Gisèle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gisèle a prêté. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gisèle range un cube. Maman ferme le portail.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Adèle prend un cube. Gisèle attend. Puis elle joue. Même leçon dehors. Prêter. Tour. Autre jeu. Maman tape dans ses mains.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Adèle veut un jouet. Que peut faire Gisèle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Gisèle a prêté. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Gisèle range un cube. Maman ferme le portail.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gisèle prête et propose un jeu</t>
+          <t>La dinette de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une tasse tape une assiette. Victorina joue à la dinette. Sarah veut la tasse bleue. Elle prête, attend, propose. Au jardin, même geste avec le cerceau et les cubes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gisèle joue à la dinette. Les tasses sont lisses. Adèle veut la tasse bleue. Maman est près de la fenêtre. Gisèle prête la tasse. Elle attend son tour. Adèle verse de l'eau imaginaire. Puis c'est le tour de Gisèle. Elle pose une assiette. On peut prêter. On attend son tour. Ou on propose un autre jeu. Plus tard, au jardin, l'herbe est tiède. Adèle veut le cerceau. On peut prêter. Ou attendre son tour. Elle prête le cerceau. Elle propose les cubes. C'est un autre jeu. Adèle prend un cube. Gisèle attend. Puis elle joue. Même leçon dehors. Prêter. Tour. Autre jeu. Maman tape dans ses mains.</t>
+          <t>Une petite tasse tape une assiette. Ding. La nappe à pois est un peu froissée. Maman essuie une cuillère. Dehors, un oiseau répète la même note. Tu as entendu le ding, Victorina ? Oui, maman. La tasse a parlé. Elle a parlé tout doux, oui. En ce moment, Victorina verse de l'eau imaginaire. Les tasses sont lisses, un peu froides. Ça sent encore le savon de la vaisselle. Le thé est prêt. Il est chaud, dans ta tête ? Un peu. Sarah s'assoit de l'autre côté de la nappe. Elle regarde la tasse bleue. Je peux la bleue ? Victorina tient la tasse un moment. Tu peux prêter, Victorina. Prêter, c'est laisser Sarah verser aussi. Puis tu attends ton tour. Tu peux. C'est ton tour. Victorina tend la tasse bleue. Sarah verse de l'eau imaginaire. Victorina attend près de maman. Elle pose une assiette ronde. Une assiette pour plus tard. Tu attends ton tour. Bravo. Sarah rend la tasse. C'est ton tour. Victorina pose la tasse sur l'assiette. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les doudous à table ? Oui. Les doudous ont faim, eux aussi. Elles asseyent deux doudous. Puis maman ouvre la porte du jardin. L'herbe est tiède. On sort un moment ? Oui. Dehors, un cerceau jaune attend près du bac. Sarah veut le cerceau. Tu te souviens, Victorina ? On peut prêter. On peut attendre son tour. Ou proposer un autre jeu. Je prête le cerceau. Puis les cubes. Sarah prend le cerceau. Victorina attend près du bac. Le bois du bac est chaud. Sarah rend le cerceau. C'est ton tour. Victorina le fait rouler une fois. Puis elle prend un cube. Sarah en prend un aussi. Même geste, autre lieu. Prêter. Tour. Autre jeu. Bravo, Victorina. Le cube est lourd ? Un peu, maman. C'est bien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gisèle joue à la dinette. Les tasses sont lisses. Adèle veut la tasse bleue. Maman est près de la fenêtre. Gisèle prête la tasse. Elle attend son tour. Adèle verse de l'eau imaginaire. Puis c'est le tour de Gisèle. Elle pose une assiette.
-maman|On peut prêter. On attend son tour. Ou on propose un autre jeu. Plus tard, au jardin, l'herbe est tiède.
-narrateur|Adèle veut le cerceau.
-enfant-f|On peut prêter. Ou attendre son tour. Elle prête le cerceau. Elle propose les cubes. C'est un autre jeu.
-narrateur|Adèle prend un cube. Gisèle attend. Puis elle joue. Même leçon dehors. Prêter. Tour. Autre jeu. Maman tape dans ses mains.</t>
+          <t>narrateur|Une petite tasse tape une assiette.
+narrateur|Ding.
+narrateur|La nappe à pois est un peu froissée.
+narrateur|Maman essuie une cuillère.
+narrateur|Dehors, un oiseau répète la même note.
+maman|Tu as entendu le ding, Victorina ?
+enfant-f|Oui, maman.
+enfant-f|La tasse a parlé.
+maman|Elle a parlé tout doux, oui.
+narrateur|En ce moment, Victorina verse de l'eau imaginaire.
+narrateur|Les tasses sont lisses, un peu froides.
+narrateur|Ça sent encore le savon de la vaisselle.
+enfant-f|Le thé est prêt.
+maman|Il est chaud, dans ta tête ?
+enfant-f|Un peu.
+narrateur|Sarah s'assoit de l'autre côté de la nappe.
+narrateur|Elle regarde la tasse bleue.
+enfant-f|Je peux la bleue ?
+narrateur|Victorina tient la tasse un moment.
+maman|Tu peux prêter, Victorina.
+maman|Prêter, c'est laisser Sarah verser aussi.
+maman|Puis tu attends ton tour.
+enfant-f|Tu peux.
+enfant-f|C'est ton tour.
+narrateur|Victorina tend la tasse bleue.
+narrateur|Sarah verse de l'eau imaginaire.
+narrateur|Victorina attend près de maman.
+narrateur|Elle pose une assiette ronde.
+enfant-f|Une assiette pour plus tard.
+maman|Tu attends ton tour.
+maman|Bravo.
+narrateur|Sarah rend la tasse.
+enfant-f|C'est ton tour.
+narrateur|Victorina pose la tasse sur l'assiette.
+maman|Tu peux proposer un autre jeu.
+maman|Un autre jeu, c'est possible.
+enfant-f|Les doudous à table ?
+maman|Oui.
+maman|Les doudous ont faim, eux aussi.
+narrateur|Elles asseyent deux doudous.
+narrateur|Puis maman ouvre la porte du jardin.
+maman|L'herbe est tiède.
+maman|On sort un moment ?
+enfant-f|Oui.
+narrateur|Dehors, un cerceau jaune attend près du bac.
+narrateur|Sarah veut le cerceau.
+maman|Tu te souviens, Victorina ?
+maman|On peut prêter.
+maman|On peut attendre son tour.
+maman|Ou proposer un autre jeu.
+enfant-f|Je prête le cerceau.
+enfant-f|Puis les cubes.
+narrateur|Sarah prend le cerceau.
+narrateur|Victorina attend près du bac.
+narrateur|Le bois du bac est chaud.
+narrateur|Sarah rend le cerceau.
+enfant-f|C'est ton tour.
+narrateur|Victorina le fait rouler une fois.
+narrateur|Puis elle prend un cube.
+narrateur|Sarah en prend un aussi.
+maman|Même geste, autre lieu.
+maman|Prêter.
+maman|Tour.
+maman|Autre jeu.
+maman|Bravo, Victorina.
+maman|Le cube est lourd ?
+enfant-f|Un peu, maman.
+maman|C'est bien.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adèle veut un jouet. Que peut faire Gisèle ?</t>
+          <t>Sarah veut un jouet. Que peut faire Victorina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1575,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Adèle veut un jouet. Que peut faire Gisèle ?</t>
+          <t>narrateur|Sarah veut un jouet.
+narrateur|Que peut faire Victorina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gisèle a prêté. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
+          <t>Victorina a prêté. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté la tasse. Puis le cerceau. Bravo. C'est du bon travail, Victorina. Les doudous ont fini le thé ? Ils ont tout bu. Un autre jeu, dehors aussi. L'herbe chatouille les chevilles. La nappe à pois attend, là-bas.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1748,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gisèle a prêté. Elle a attendu son tour. Elle a proposé un autre jeu.</t>
+          <t>narrateur|Victorina a prêté.
+narrateur|Elle a attendu son tour.
+narrateur|Elle a proposé un autre jeu.
+maman|Tu as prêté la tasse.
+maman|Puis le cerceau.
+maman|Bravo.
+maman|C'est du bon travail, Victorina.
+maman|Les doudous ont fini le thé ?
+enfant-f|Ils ont tout bu.
+maman|Un autre jeu, dehors aussi.
+narrateur|L'herbe chatouille les chevilles.
+narrateur|La nappe à pois attend, là-bas.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1787,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gisèle range un cube. Maman ferme le portail.</t>
+          <t>Victorina range un cube dans le bac. Maman ferme le portail. Le cerceau rentre aussi ? Oui, maman. Le cerceau tape le mur, tout léger. Tes genoux ont un peu d'herbe. On les essuie ? Oui. Le torchon sent le savon. Merci d'avoir prêté. Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1923,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gisèle range un cube. Maman ferme le portail.</t>
+          <t>narrateur|Victorina range un cube dans le bac.
+narrateur|Maman ferme le portail.
+maman|Le cerceau rentre aussi ?
+enfant-f|Oui, maman.
+narrateur|Le cerceau tape le mur, tout léger.
+maman|Tes genoux ont un peu d'herbe.
+maman|On les essuie ?
+enfant-f|Oui.
+narrateur|Le torchon sent le savon.
+maman|Merci d'avoir prêté.
+maman|Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai prêté. Puis un autre jeu. Bravo. Tu as fait du bon travail. La petite tasse reste sur l'assiette. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2101,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai prêté.
+enfant-f|Puis un autre jeu.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La petite tasse reste sur l'assiette.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-07.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gisèle joue à la dinette. Les tasses sont lisses. Adèle veut la tasse bleue. Maman est près de la fenêtre. Gisèle prête la tasse. Elle attend son tour. Adèle verse de l'eau imaginaire. Puis c'est le tour de Gisèle. Elle pose une assiette. Maman dit : on peut &lt;emphasis level="moderate"&gt;prêter&lt;/emphasis&gt;. On attend son tour. Ou on propose un autre jeu. Plus tard, au jardin, l'herbe est tiède. Adèle veut le cerceau. Gisèle dit : on peut prêter. Ou attendre son tour. Elle prête le cerceau. Elle propose les cubes. C'est un autre jeu. Adèle prend un cube. Gisèle attend. Puis elle joue. Même leçon dehors. Prêter. Tour. Autre jeu. Maman tape dans ses mains.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une petite tasse tape une assiette. Ding. La nappe à pois est un peu froissée. Maman essuie une cuillère. Dehors, un oiseau répète la même note. Tu as entendu le ding, Victorina ? Oui, maman. La tasse a parlé. Elle a parlé tout doux, oui. En ce moment, Victorina verse de l'eau imaginaire. Les tasses sont lisses, un peu froides. Ça sent encore le savon de la vaisselle. Le thé est prêt. Il est chaud, dans ta tête ? Un peu. Sarah s'assoit de l'autre côté de la nappe. Elle regarde la tasse bleue. Je peux la bleue ? Victorina tient la tasse un moment. Tu peux prêter, Victorina. Prêter, c'est laisser Sarah verser aussi. Puis tu attends ton tour. Tu peux. C'est ton tour. Victorina tend la tasse bleue. Sarah verse de l'eau imaginaire. Victorina attend près de maman. Elle pose une assiette ronde. Une assiette pour plus tard. Tu attends ton tour. Bravo. Sarah rend la tasse. C'est ton tour. Victorina pose la tasse sur l'assiette. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les doudous à table ? Oui. Les doudous ont faim, eux aussi. Elles asseyent deux doudous. Puis maman ouvre la porte du jardin. L'herbe est tiède. On sort un moment ? Oui. Dehors, un cerceau jaune attend près du bac. Sarah veut le cerceau. Tu te souviens, Victorina ? On peut prêter. On peut attendre son tour. Ou proposer un autre jeu. Je prête le cerceau. Puis les cubes. Sarah prend le cerceau. Victorina attend près du bac. Le bois du bac est chaud. Sarah rend le cerceau. C'est ton tour. Victorina le fait rouler une fois. Puis elle prend un cube. Sarah en prend un aussi. Même geste, autre lieu. Prêter. Tour. Autre jeu. Bravo, Victorina. Le cube est lourd ? Un peu, maman. C'est bien.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1394,7 +1394,6 @@
 maman|C'est bien.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1424,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adèle veut un jouet. Que peut faire Gisèle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah veut un jouet. Que peut faire Victorina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1579,7 +1578,6 @@
 narrateur|Que peut faire Victorina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1604,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a prêté. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté la tasse. Puis le cerceau. Bravo. C'est du bon travail, Victorina. Les doudous ont fini le thé ? Ils ont tout bu. Un autre jeu, dehors aussi. L'herbe chatouille les chevilles. La nappe à pois attend, là-bas.</t>
+          <t>Victorina a prêté. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté la tasse. Puis le cerceau. Bravo. Les doudous ont fini le thé ? Ils ont tout bu. Un autre jeu, dehors aussi. L'herbe chatouille les chevilles. La nappe à pois attend, là-bas.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gisèle a prêté. Elle a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Elle a proposé un autre jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a prêté. Elle a attendu son tour. Elle a proposé un autre jeu. Tu as prêté la tasse. Puis le cerceau. Bravo. Les doudous ont fini le thé ? Ils ont tout bu. Un autre jeu, dehors aussi. L'herbe chatouille les chevilles. La nappe à pois attend, là-bas.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,7 +1752,6 @@
 maman|Tu as prêté la tasse.
 maman|Puis le cerceau.
 maman|Bravo.
-maman|C'est du bon travail, Victorina.
 maman|Les doudous ont fini le thé ?
 enfant-f|Ils ont tout bu.
 maman|Un autre jeu, dehors aussi.
@@ -1762,7 +1759,6 @@
 narrateur|La nappe à pois attend, là-bas.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1792,7 +1788,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gisèle range un cube. Maman ferme le portail.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina range un cube dans le bac. Maman ferme le portail. Le cerceau rentre aussi ? Oui, maman. Le cerceau tape le mur, tout léger. Tes genoux ont un peu d'herbe. On les essuie ? Oui. Le torchon sent le savon. Merci d'avoir prêté. Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1932,6 @@
 maman|Merci d'avoir attendu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai prêté. Puis un autre jeu. Bravo. Tu as fait du bon travail. La petite tasse reste sur l'assiette. L'histoire est finie.</t>
+          <t>J'ai prêté. Puis un autre jeu. Bravo. La petite tasse reste sur l'assiette.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai prêté. Puis un autre jeu. Bravo. La petite tasse reste sur l'assiette.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,12 +2099,9 @@
           <t>enfant-f|J'ai prêté.
 enfant-f|Puis un autre jeu.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La petite tasse reste sur l'assiette.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La petite tasse reste sur l'assiette.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gisèle, Adèle, maman</t>
+          <t>Victorina, Sarah, maman</t>
         </is>
       </c>
     </row>
